--- a/artfynd/A 60805-2022 artfynd.xlsx
+++ b/artfynd/A 60805-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60805-2022 artfynd.xlsx
+++ b/artfynd/A 60805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2167,117 +2167,6 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>114461498</v>
-      </c>
-      <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>sydost Buckarby, Upl</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>612588</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6674777</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>C-Heb-0299</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Olof Hedgren</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60805-2022 artfynd.xlsx
+++ b/artfynd/A 60805-2022 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73910392</v>
+        <v>73910381</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>sydost Buckarby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612594.0621147978</v>
+        <v>612492</v>
       </c>
       <c r="R2" t="n">
-        <v>6674813.647766102</v>
+        <v>6674789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,21 +743,11 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73910389</v>
+        <v>73910380</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612584.1214463688</v>
+        <v>612598</v>
       </c>
       <c r="R3" t="n">
-        <v>6674731.734838955</v>
+        <v>6674830</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +850,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73910391</v>
+        <v>73910389</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612588.7392864884</v>
+        <v>612584</v>
       </c>
       <c r="R4" t="n">
-        <v>6674840.851823254</v>
+        <v>6674732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,19 +957,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73910380</v>
+        <v>73910391</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612598.0542377969</v>
+        <v>612589</v>
       </c>
       <c r="R5" t="n">
-        <v>6674829.69372339</v>
+        <v>6674841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1064,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73910388</v>
+        <v>73910383</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>612619.300410821</v>
+        <v>612491</v>
       </c>
       <c r="R6" t="n">
-        <v>6674722.367445537</v>
+        <v>6674673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,19 +1176,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73910383</v>
+        <v>73910387</v>
       </c>
       <c r="B7" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612490.7365154601</v>
+        <v>612619</v>
       </c>
       <c r="R7" t="n">
-        <v>6674672.632833036</v>
+        <v>6674722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,19 +1288,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73910384</v>
+        <v>73910392</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612490.7365154601</v>
+        <v>612594</v>
       </c>
       <c r="R8" t="n">
-        <v>6674672.632833036</v>
+        <v>6674814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1500,19 +1400,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,15 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73910393</v>
+        <v>73910384</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612594.0621147978</v>
+        <v>612491</v>
       </c>
       <c r="R9" t="n">
-        <v>6674813.647766102</v>
+        <v>6674673</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,19 +1512,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,50 +1551,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73910381</v>
+        <v>73910388</v>
       </c>
       <c r="B10" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>366</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>sydost Buckarby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612491.6576140448</v>
+        <v>612619</v>
       </c>
       <c r="R10" t="n">
-        <v>6674788.604031265</v>
+        <v>6674722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,21 +1624,11 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1645,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1798,15 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73910382</v>
+        <v>73910393</v>
       </c>
       <c r="B11" t="n">
-        <v>4808</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101675</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1843,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612491.6576140448</v>
+        <v>612594</v>
       </c>
       <c r="R11" t="n">
-        <v>6674788.604031265</v>
+        <v>6674814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,21 +1736,11 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1907,7 +1757,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>asphögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1925,15 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73910387</v>
+        <v>73910382</v>
       </c>
       <c r="B12" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>101675</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1970,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>612619.300410821</v>
+        <v>612492</v>
       </c>
       <c r="R12" t="n">
-        <v>6674722.367445537</v>
+        <v>6674789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2003,21 +1848,11 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2034,7 +1869,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>asphögstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2055,12 +1890,7 @@
         <v>73910390</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2092,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>612587.7245838109</v>
+        <v>612588</v>
       </c>
       <c r="R13" t="n">
-        <v>6674776.6302913</v>
+        <v>6674777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2125,19 +1955,9 @@
           <t>2018-10-31</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60805-2022 artfynd.xlsx
+++ b/artfynd/A 60805-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910389</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910387</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910384</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910388</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910393</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910382</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,8 +2046,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73910390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>